--- a/web/public/forms/orig/o-gondola-check.xlsx
+++ b/web/public/forms/orig/o-gondola-check.xlsx
@@ -886,7 +886,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="19" t="inlineStr">

--- a/web/public/forms/orig/o-gondola-check.xlsx
+++ b/web/public/forms/orig/o-gondola-check.xlsx
@@ -8,13 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="곤돌라 점검표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'곤돌라 점검표'!$7:$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'곤돌라 점검표'!$A$1:$H$27</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'작성 예시'!$7:$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -191,9 +188,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,161 +266,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>47625</colOff>
-      <row>9</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <ext cx="1638300" cy="933450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>152400</colOff>
-      <row>10</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <ext cx="1419225" cy="1019175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>171450</colOff>
-      <row>11</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <ext cx="1371600" cy="1019175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>47625</colOff>
-      <row>15</row>
-      <rowOff>285750</rowOff>
-    </from>
-    <ext cx="1638300" cy="1638300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>171450</colOff>
-      <row>21</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <ext cx="1381125" cy="1019175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>180975</colOff>
-      <row>22</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <ext cx="1352550" cy="1019175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -968,10 +807,7 @@
           <t>판    정</t>
         </is>
       </c>
-      <c r="H5" s="10">
-        <f>IF(COUNTA(G8:G25)=0,"",IF(COUNTIF(G8:G25,"불량")&gt;0,"사용 중지","사용 가능"))</f>
-        <v/>
-      </c>
+      <c r="H5" s="10" t="n"/>
     </row>
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="24" customHeight="1">
@@ -1363,16 +1199,14 @@
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
-      <c r="C27" s="17">
-        <f>IF(COUNTA(G8:G25)=0,"","양호 "&amp;COUNTIF(G8:G25,"양호")&amp;" · 불량 "&amp;COUNTIF(G8:G25,"불량")&amp;" · 해당없음 "&amp;COUNTIF(G8:G25,"해당없음")&amp;" · 빈칸 "&amp;COUNTBLANK(G8:G25)&amp;"  (모두 "&amp;ROWS(G8:G25)&amp;"칸)")</f>
-        <v/>
-      </c>
+      <c r="C27" s="17" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
@@ -1440,649 +1274,4 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1"/>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>■ 곤돌라 체크리스트</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>점  검  자</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>점검 일자</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="7" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>장비 번호</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>GD-02 (250kg)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>운 전 원</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>김운전  (인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>관리감독자</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>이감독  (인)</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>안전관리자</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>박안전  (인)</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>판    정</t>
-        </is>
-      </c>
-      <c r="H5" s="10">
-        <f>IF(COUNTA(G8:G25)=0,"",IF(COUNTIF(G8:G25,"불량")&gt;0,"사용 중지","사용 가능"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="6" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>구 분</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>예 시 사 진</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>점 검 기 준</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>점 검 항 목</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>결 과</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>조 치 사 항</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>곤돌라
-제원표</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>곤돌라 제원표를 확인할 것</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>- 곤돌라의 제원표 부착 여부 확인</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>- 제원의 적재중량(최대중량)이상 적재여부 확인</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="n"/>
-    </row>
-    <row r="10" ht="88" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>권과방지
-장치</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>곤돌라 권과방지장치 작동상태를 확인할 것</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>- 필요이상 상승할 경우 경보음과 함께 작동 정지 여부 확인</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="n"/>
-    </row>
-    <row r="11" ht="88" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>과부하
-방지장치</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>곤돌라 과부하방지장치 작동상태를 확인할 것</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>- 정격하중의 1.1배 이상의 하중 권상시 경보와 함께 권상동작 정지여부 확인</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="n"/>
-    </row>
-    <row r="12" ht="29.33333333333334" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>비상정지
-장치</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>비상정지장치 설치 및 작동 확인</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>- 적색 누름버튼 설치 확인</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="29.33333333333334" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>- 수동 복귀 여부 확인</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="29.33333333333334" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>- 정상작동 여부 확인</t>
-        </is>
-      </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>와이어
-로프 및
-블럭스톱</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>주와이어로프, 보조와이어 및 블럭스톱의 상태를 확인할 것</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>- 이음매가 있는 와이어로프 사용금지 여부 확인</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="42.5" customHeight="1">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>- 지름의 감소가 공칭지름의 7퍼센트를 초과하는 와이어로프 사용금지 여부 확인</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>- 꼬인 와이어로프 사용금지 여부 확인</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>- 심하게 변형 또는 부식된 와이어로프 사용금지 여부 확인</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="42.5" customHeight="1">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>- 1꼬임 사이에서 소선의 수가 10퍼센트 이상 절단 와이어로프 사용금지 여부 확인</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="17.5" customHeight="1">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>- 와이어로프 단말처리 여부 확인</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="42.5" customHeight="1">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>- 주와이어가 손상되었을 경우 블록스톱이 보조와이어로프를 잡아주는지 여부 확인</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="n"/>
-    </row>
-    <row r="22" ht="88" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>수평
-조정장치</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>수평조정장치의 상태를 확인할 것</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>- 수평조정장치 정상 작동여부 확인</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="37.66666666666666" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>안전조치</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>낙하물방어조치 및 추락 방어조치를 확인할 것</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>- 발끝막이판의 높이가 10cm이상 여부 확인</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>불량</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>발끝막이판 보강(10cm) 후 재점검</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25.16666666666667" customHeight="1">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>- 높이 90cm이상 난간대 설치 확인</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="n"/>
-    </row>
-    <row r="25" ht="25.16666666666667" customHeight="1">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>- 생명줄 설치여부 확인</t>
-        </is>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>양호</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="n"/>
-    </row>
-    <row r="26" ht="6" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>점 검 결 과</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="17">
-        <f>IF(COUNTA(G8:G25)=0,"","양호 "&amp;COUNTIF(G8:G25,"양호")&amp;" · 불량 "&amp;COUNTIF(G8:G25,"불량")&amp;" · 해당없음 "&amp;COUNTIF(G8:G25,"해당없음")&amp;" · 빈칸 "&amp;COUNTBLANK(G8:G25)&amp;"  (모두 "&amp;ROWS(G8:G25)&amp;"칸)")</f>
-        <v/>
-      </c>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 장비·회사·이름).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B15:B21"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="C15:D21"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A15:A21"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="C12:D14"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C23:D25"/>
-    <mergeCell ref="E15:E21"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"양호,불량,해당없음"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.3" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/web/public/forms/orig/o-gondola-check.xlsx
+++ b/web/public/forms/orig/o-gondola-check.xlsx
@@ -725,7 +725,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
